--- a/关键词.xlsx
+++ b/关键词.xlsx
@@ -27,825 +27,597 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="273">
-  <si>
-    <t>rocket games</t>
-  </si>
-  <si>
-    <t>rocket goal</t>
-  </si>
-  <si>
-    <t>rocket league unblocked</t>
-  </si>
-  <si>
-    <t>rocketgoal</t>
-  </si>
-  <si>
-    <t>rocket soccer</t>
-  </si>
-  <si>
-    <t>rocket goal.io</t>
-  </si>
-  <si>
-    <t>rocketgames</t>
-  </si>
-  <si>
-    <t>rocket goal io</t>
-  </si>
-  <si>
-    <t>rocketgoal.io</t>
-  </si>
-  <si>
-    <t>rocketpult</t>
-  </si>
-  <si>
-    <t>rocket goal unblocked</t>
-  </si>
-  <si>
-    <t>rocket goal io cheats</t>
-  </si>
-  <si>
-    <t>rcoket goal</t>
-  </si>
-  <si>
-    <t>rocket pult</t>
-  </si>
-  <si>
-    <t>rocket ball</t>
-  </si>
-  <si>
-    <t>rocket league online</t>
-  </si>
-  <si>
-    <t>rocket goal i.o</t>
-  </si>
-  <si>
-    <t>roket goal</t>
-  </si>
-  <si>
-    <t>roket games</t>
-  </si>
-  <si>
-    <t>rockrt games</t>
-  </si>
-  <si>
-    <t>rocketgoal io</t>
-  </si>
-  <si>
-    <t>goaloo</t>
-  </si>
-  <si>
-    <t>rocket league io</t>
-  </si>
-  <si>
-    <t>rocketgames.io</t>
-  </si>
-  <si>
-    <t>rocket games io</t>
-  </si>
-  <si>
-    <t>rocket league soccer game</t>
-  </si>
-  <si>
-    <t>rocket goal .io</t>
-  </si>
-  <si>
-    <t>gol.gg</t>
-  </si>
-  <si>
-    <t>rocketball</t>
-  </si>
-  <si>
-    <t>rocket goal game</t>
-  </si>
-  <si>
-    <t>rocket league.io</t>
-  </si>
-  <si>
-    <t>rocket i.o</t>
-  </si>
-  <si>
-    <t>ball io</t>
-  </si>
-  <si>
-    <t>rocket cars</t>
-  </si>
-  <si>
-    <t>rocket league 2d unblocked</t>
-  </si>
-  <si>
-    <t>rocket io</t>
-  </si>
-  <si>
-    <t>ocket</t>
-  </si>
-  <si>
-    <t>roct</t>
-  </si>
-  <si>
-    <t>rockety</t>
-  </si>
-  <si>
-    <t>rocket car game</t>
-  </si>
-  <si>
-    <t>rocket games'</t>
-  </si>
-  <si>
-    <t>goles.com</t>
-  </si>
-  <si>
-    <t>rocket league online free</t>
-  </si>
-  <si>
-    <t>rocket league online game</t>
-  </si>
-  <si>
-    <t>rocket goal .io unblocked</t>
-  </si>
-  <si>
-    <t>rocket goal classroom</t>
-  </si>
-  <si>
-    <t>rocket games.io</t>
-  </si>
-  <si>
-    <t>rocket.goal</t>
-  </si>
-  <si>
-    <t>rocketgal</t>
-  </si>
-  <si>
-    <t>rocket ball game</t>
-  </si>
-  <si>
-    <t>roketgoal</t>
-  </si>
-  <si>
-    <t>unblocked games rocket league</t>
-  </si>
-  <si>
-    <t>rocket ball golf</t>
-  </si>
-  <si>
-    <t>rocket car ball</t>
-  </si>
-  <si>
-    <t>rocket league unblocked game</t>
-  </si>
-  <si>
-    <t>rocketsoccer</t>
-  </si>
-  <si>
-    <t>rocketgoal.io unblocked</t>
-  </si>
-  <si>
-    <t>soccer cars unblocked</t>
-  </si>
-  <si>
-    <t>rocket league web</t>
-  </si>
-  <si>
-    <t>rocket league goal</t>
-  </si>
-  <si>
-    <t>rocket games online</t>
-  </si>
-  <si>
-    <t>soccer game like rocket league</t>
-  </si>
-  <si>
-    <t>rocketgoal unblocked</t>
-  </si>
-  <si>
-    <t>rocket league unblocked games</t>
-  </si>
-  <si>
-    <t>rocket league games unblocked</t>
-  </si>
-  <si>
-    <t>fake rocket league game</t>
-  </si>
-  <si>
-    <t>rocket league browser</t>
-  </si>
-  <si>
-    <t>rocket league .io</t>
-  </si>
-  <si>
-    <t>rocketcar</t>
-  </si>
-  <si>
-    <t>trgoal</t>
-  </si>
-  <si>
-    <t>rocketgaol</t>
-  </si>
-  <si>
-    <t>rocket.io</t>
-  </si>
-  <si>
-    <t>soccer game with cars</t>
-  </si>
-  <si>
-    <t>rocket goal classroom 6x</t>
-  </si>
-  <si>
-    <t>classroom 6x rocket goal</t>
-  </si>
-  <si>
-    <t>rocketcar game</t>
-  </si>
-  <si>
-    <t>knockoff rocket league</t>
-  </si>
-  <si>
-    <t>rocket gaol</t>
-  </si>
-  <si>
-    <t>rocket goal . io</t>
-  </si>
-  <si>
-    <t>soccer.io</t>
-  </si>
-  <si>
-    <t>rocketgoal classroom</t>
-  </si>
-  <si>
-    <t>ball io game</t>
-  </si>
-  <si>
-    <t>rocket league crazy games</t>
-  </si>
-  <si>
-    <t>rocketgoal io unblocked</t>
-  </si>
-  <si>
-    <t>rocket goal hacks</t>
-  </si>
-  <si>
-    <t>rocket goal crazy games</t>
-  </si>
-  <si>
-    <t>goall</t>
-  </si>
-  <si>
-    <t>rocket soccer unblocked</t>
-  </si>
-  <si>
-    <t>rocket league goals</t>
-  </si>
-  <si>
-    <t>car io game</t>
-  </si>
-  <si>
-    <t>rocketer io</t>
-  </si>
-  <si>
-    <t>rocketleague.io</t>
-  </si>
-  <si>
-    <t>rocket league rip off</t>
-  </si>
-  <si>
-    <t>car with rocket</t>
-  </si>
-  <si>
-    <t>rocketgame</t>
-  </si>
-  <si>
-    <t>rocket goal.io unblocked</t>
-  </si>
-  <si>
-    <t>soccer rocket league game</t>
-  </si>
-  <si>
-    <t>rocket ganes</t>
-  </si>
-  <si>
-    <t>free rocket league online</t>
-  </si>
-  <si>
-    <t>soccer rocket</t>
-  </si>
-  <si>
-    <t>rocket leauge io</t>
-  </si>
-  <si>
-    <t>rocket .io</t>
-  </si>
-  <si>
-    <t>rocketpult game</t>
-  </si>
-  <si>
-    <t>rockegoal</t>
-  </si>
-  <si>
-    <t>rocket goal g+</t>
-  </si>
-  <si>
-    <t>rocket gold.io</t>
-  </si>
-  <si>
-    <t>crazy games rocket league</t>
-  </si>
-  <si>
-    <t>rocket gol</t>
-  </si>
-  <si>
-    <t>rocketleague io</t>
-  </si>
-  <si>
-    <t>rocket goal classroom center</t>
-  </si>
-  <si>
-    <t>rocket cars game</t>
-  </si>
-  <si>
-    <t>1v1 soccer io</t>
-  </si>
-  <si>
-    <t>rocket league school game</t>
-  </si>
-  <si>
-    <t>rocket gola</t>
-  </si>
-  <si>
-    <t>soccer i.o</t>
-  </si>
-  <si>
-    <t>car.io</t>
-  </si>
-  <si>
-    <t>rocket goal unlocked</t>
-  </si>
-  <si>
-    <t>gooool.org</t>
-  </si>
-  <si>
-    <t>rockat games</t>
-  </si>
-  <si>
-    <t>rocket game io</t>
-  </si>
-  <si>
-    <t>rocketgo</t>
-  </si>
-  <si>
-    <t>goal4</t>
-  </si>
-  <si>
-    <t>rocket leugue unblocked</t>
-  </si>
-  <si>
-    <t>rocketgoa</t>
-  </si>
-  <si>
-    <t>rocket league car game</t>
-  </si>
-  <si>
-    <t>roket ball</t>
-  </si>
-  <si>
-    <t>roket goal.io</t>
-  </si>
-  <si>
-    <t>goal unlimited</t>
-  </si>
-  <si>
-    <t>yo play.io</t>
-  </si>
-  <si>
-    <t>game soccer with cars</t>
-  </si>
-  <si>
-    <t>rocket goal.io classroom</t>
-  </si>
-  <si>
-    <t>rocket soccer github</t>
-  </si>
-  <si>
-    <t>rocket game.io</t>
-  </si>
-  <si>
-    <t>rocket goal io unblocked</t>
-  </si>
-  <si>
-    <t>rocket soccer league</t>
-  </si>
-  <si>
-    <t>rockit rocker</t>
-  </si>
-  <si>
-    <t>gol lol</t>
-  </si>
-  <si>
-    <t>rockergoal</t>
-  </si>
-  <si>
-    <t>rockot</t>
-  </si>
-  <si>
-    <t>rocket gaming</t>
-  </si>
-  <si>
-    <t>rocket league in browser</t>
-  </si>
-  <si>
-    <t>gold golas</t>
-  </si>
-  <si>
-    <t>rocket league online free play</t>
-  </si>
-  <si>
-    <t>crazygames car</t>
-  </si>
-  <si>
-    <t>goaql</t>
-  </si>
-  <si>
-    <t>rocket league browser game</t>
-  </si>
-  <si>
-    <t>roccat download</t>
-  </si>
-  <si>
-    <t>goual</t>
-  </si>
-  <si>
-    <t>rocket game online</t>
-  </si>
-  <si>
-    <t>cars.io</t>
-  </si>
-  <si>
-    <t>rocket games com</t>
-  </si>
-  <si>
-    <t>roocket</t>
-  </si>
-  <si>
-    <t>рокет</t>
-  </si>
-  <si>
-    <t>roketgames</t>
-  </si>
-  <si>
-    <t>carball.io</t>
-  </si>
-  <si>
-    <t>soccer io games</t>
-  </si>
-  <si>
-    <t>gaole</t>
-  </si>
-  <si>
-    <t>rocketg</t>
-  </si>
-  <si>
-    <t>turbo goal</t>
-  </si>
-  <si>
-    <t>oo gol</t>
-  </si>
-  <si>
-    <t>4goal</t>
-  </si>
-  <si>
-    <t>rocket league ios</t>
-  </si>
-  <si>
-    <t>rocket soocer</t>
-  </si>
-  <si>
-    <t>rocket league free online game</t>
-  </si>
-  <si>
-    <t>unbanned g+ game</t>
-  </si>
-  <si>
-    <t>rocket league game free online</t>
-  </si>
-  <si>
-    <t>rocket car soccer</t>
-  </si>
-  <si>
-    <t>rocket leage online</t>
-  </si>
-  <si>
-    <t>rocket league for ios</t>
-  </si>
-  <si>
-    <t>rocket leauge online</t>
-  </si>
-  <si>
-    <t>io4 ion</t>
-  </si>
-  <si>
-    <t>rokel</t>
-  </si>
-  <si>
-    <t>lio and galo</t>
-  </si>
-  <si>
-    <t>online multiplayer car games</t>
-  </si>
-  <si>
-    <t>juegos poki de fútbol</t>
-  </si>
-  <si>
-    <t>games rocket</t>
-  </si>
-  <si>
-    <t>rocket ion</t>
-  </si>
-  <si>
-    <t>rocket soccer gitlab</t>
-  </si>
-  <si>
-    <t>rocket go</t>
-  </si>
-  <si>
-    <t>goal to goal</t>
-  </si>
-  <si>
-    <t>socer io</t>
-  </si>
-  <si>
-    <t>rocket league website game</t>
-  </si>
-  <si>
-    <t>rocket league web game</t>
-  </si>
-  <si>
-    <t>goail</t>
-  </si>
-  <si>
-    <t>rockey games</t>
-  </si>
-  <si>
-    <t>car .io</t>
-  </si>
-  <si>
-    <t>rocket goal online</t>
-  </si>
-  <si>
-    <t>rocket goal free</t>
-  </si>
-  <si>
-    <t>rocket goal free online</t>
-  </si>
-  <si>
-    <t>rocket goal unblocked 66</t>
-  </si>
-  <si>
-    <t>rocket goal unblocked 76</t>
-  </si>
-  <si>
-    <t>play rocket goal</t>
-  </si>
-  <si>
-    <t>rocket goal io game</t>
-  </si>
-  <si>
-    <t>rocket goal browser game</t>
-  </si>
-  <si>
-    <t>rocket goal soccer game</t>
-  </si>
-  <si>
-    <t>rocket goal football game</t>
-  </si>
-  <si>
-    <t>rocket goal multiplayer</t>
-  </si>
-  <si>
-    <t>rocket goal mobile</t>
-  </si>
-  <si>
-    <t>rocket goal apk</t>
-  </si>
-  <si>
-    <t>rocket goal download</t>
-  </si>
-  <si>
-    <t>rocket goal latest version</t>
-  </si>
-  <si>
-    <t>rocket goal update</t>
-  </si>
-  <si>
-    <t>rocket goal review</t>
-  </si>
-  <si>
-    <t>rocket goal wiki</t>
-  </si>
-  <si>
-    <t>rocket goal github</t>
-  </si>
-  <si>
-    <t>rocket goal cheats</t>
-  </si>
-  <si>
-    <t>rocket goal ranks</t>
-  </si>
-  <si>
-    <t>rocket goal leaderboard</t>
-  </si>
-  <si>
-    <t>rocket goal ranking system</t>
-  </si>
-  <si>
-    <t>rocket goal gameplay</t>
-  </si>
-  <si>
-    <t>rocket goal controls</t>
-  </si>
-  <si>
-    <t>rocket goal guide</t>
-  </si>
-  <si>
-    <t>rocket goal tips</t>
-  </si>
-  <si>
-    <t>rocket goal strategy</t>
-  </si>
-  <si>
-    <t>rocket goal how to play</t>
-  </si>
-  <si>
-    <t>rocket goal best car</t>
-  </si>
-  <si>
-    <t>rocket goal crazygames</t>
-  </si>
-  <si>
-    <t>rocket goal poki</t>
-  </si>
-  <si>
-    <t>rocket goal online free</t>
-  </si>
-  <si>
-    <t>rocket goal browser</t>
-  </si>
-  <si>
-    <t>rocket goal no download</t>
-  </si>
-  <si>
-    <t>rocket games free</t>
-  </si>
-  <si>
-    <t>rocket games unblocked</t>
-  </si>
-  <si>
-    <t>rocket games multiplayer</t>
-  </si>
-  <si>
-    <t>rocket games no download</t>
-  </si>
-  <si>
-    <t>rocket games browser</t>
-  </si>
-  <si>
-    <t>rocket games for kids</t>
-  </si>
-  <si>
-    <t>rocket games crazy games</t>
-  </si>
-  <si>
-    <t>rocket games poki</t>
-  </si>
-  <si>
-    <t>rocket ship games</t>
-  </si>
-  <si>
-    <t>rocket racing games</t>
-  </si>
-  <si>
-    <t>rocket football games</t>
-  </si>
-  <si>
-    <t>rocket soccer games</t>
-  </si>
-  <si>
-    <t>rocket car games</t>
-  </si>
-  <si>
-    <t>rocket league</t>
-  </si>
-  <si>
-    <t>rocket league goal songs</t>
-  </si>
-  <si>
-    <t>rocket league goal anthem</t>
-  </si>
-  <si>
-    <t>rocket league goal anthem songs</t>
-  </si>
-  <si>
-    <t>rocket league goal music</t>
-  </si>
-  <si>
-    <t>rocket league goal celebration</t>
-  </si>
-  <si>
-    <t>rocket league goal explosions</t>
-  </si>
-  <si>
-    <t>goal explosions rocket league</t>
-  </si>
-  <si>
-    <t>rocket league best goal explosions</t>
-  </si>
-  <si>
-    <t>rocket league goal explosion</t>
-  </si>
-  <si>
-    <t>rocket league goal explosion list</t>
-  </si>
-  <si>
-    <t>rocket league goal explosion tier list</t>
-  </si>
-  <si>
-    <t>rocket league goal explosion prices</t>
-  </si>
-  <si>
-    <t>rocket league goal explosion trading</t>
-  </si>
-  <si>
-    <t>rocket league splash goal explosion</t>
-  </si>
-  <si>
-    <t>rocket league spongebob goal explosion</t>
-  </si>
-  <si>
-    <t>rocket league swish goal</t>
-  </si>
-  <si>
-    <t>rocket league aerial goal</t>
-  </si>
-  <si>
-    <t>rocket league aerial goal tutorial</t>
-  </si>
-  <si>
-    <t>rocket league aerial goal training</t>
-  </si>
-  <si>
-    <t>rocket league scoring goals</t>
-  </si>
-  <si>
-    <t>rocket league own goal</t>
-  </si>
-  <si>
-    <t>rocket league bicycle goal</t>
-  </si>
-  <si>
-    <t>rocket league rare goal explosions</t>
-  </si>
-  <si>
-    <t>rocket league black market goal explosions</t>
-  </si>
-  <si>
-    <t>rocket league tournament goal explosion</t>
-  </si>
-  <si>
-    <t>rocket league best goal anthem</t>
-  </si>
-  <si>
-    <t>rocket league custom goal songs</t>
-  </si>
-  <si>
-    <t>ronaldo rocket goal</t>
-  </si>
-  <si>
-    <t>rocket goal in football</t>
-  </si>
-  <si>
-    <t>rocket goal soccer</t>
-  </si>
-  <si>
-    <t>rocket goal meaning</t>
-  </si>
-  <si>
-    <t>rocket goal highlights</t>
-  </si>
-  <si>
-    <t>ronaldo rocket goal video</t>
-  </si>
-  <si>
-    <t>ronaldo long range goal</t>
-  </si>
-  <si>
-    <t>best rocket goals in football</t>
-  </si>
-  <si>
-    <t>rocket shot goal</t>
-  </si>
-  <si>
-    <t>top rocket goals</t>
-  </si>
-  <si>
-    <t>rocket strike goal</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="197">
+  <si>
+    <t>coreball</t>
+  </si>
+  <si>
+    <t>core ball</t>
+  </si>
+  <si>
+    <t>core ball game</t>
+  </si>
+  <si>
+    <t>coreball game</t>
+  </si>
+  <si>
+    <t>corball</t>
+  </si>
+  <si>
+    <t>core ball unblocked</t>
+  </si>
+  <si>
+    <t>coreball unblocked</t>
+  </si>
+  <si>
+    <t>coreball monkey type</t>
+  </si>
+  <si>
+    <t>core ball monkey type</t>
+  </si>
+  <si>
+    <t>coerball</t>
+  </si>
+  <si>
+    <t>monkey type core ball</t>
+  </si>
+  <si>
+    <t>core ball online</t>
+  </si>
+  <si>
+    <t>monkeytype core ball</t>
+  </si>
+  <si>
+    <t>coreball a real me</t>
+  </si>
+  <si>
+    <t>core balll</t>
+  </si>
+  <si>
+    <t>core vall</t>
+  </si>
+  <si>
+    <t>coreballl</t>
+  </si>
+  <si>
+    <t>ezclassroom</t>
+  </si>
+  <si>
+    <t>cor ball</t>
+  </si>
+  <si>
+    <t>core ball game unblocked</t>
+  </si>
+  <si>
+    <t>core ball not blocked</t>
+  </si>
+  <si>
+    <t>coreba</t>
+  </si>
+  <si>
+    <t>coreboll</t>
+  </si>
+  <si>
+    <t>coreball game unblocked</t>
+  </si>
+  <si>
+    <t>core ball scratch</t>
+  </si>
+  <si>
+    <t>coreball arealme</t>
+  </si>
+  <si>
+    <t>core balls</t>
+  </si>
+  <si>
+    <t>coreball level 100</t>
+  </si>
+  <si>
+    <t>arealme core ball</t>
+  </si>
+  <si>
+    <t>coreball online</t>
+  </si>
+  <si>
+    <t>corball game</t>
+  </si>
+  <si>
+    <t>p 1234</t>
+  </si>
+  <si>
+    <t>core ball level 100</t>
+  </si>
+  <si>
+    <t>core ball github</t>
+  </si>
+  <si>
+    <t>pin circle</t>
+  </si>
+  <si>
+    <t>coreball.com</t>
+  </si>
+  <si>
+    <t>coreball github</t>
+  </si>
+  <si>
+    <t>play core ball</t>
+  </si>
+  <si>
+    <t>core ball unblocked 76</t>
+  </si>
+  <si>
+    <t>corebll</t>
+  </si>
+  <si>
+    <t>core ball online play coreball game</t>
+  </si>
+  <si>
+    <t>a real me coreball</t>
+  </si>
+  <si>
+    <t>core.ball</t>
+  </si>
+  <si>
+    <t>pin circle game</t>
+  </si>
+  <si>
+    <t>core ball batman</t>
+  </si>
+  <si>
+    <t>pin the circle</t>
+  </si>
+  <si>
+    <t>core ball 2</t>
+  </si>
+  <si>
+    <t>google core ball</t>
+  </si>
+  <si>
+    <t>play coreball</t>
+  </si>
+  <si>
+    <t>skill arcade games</t>
+  </si>
+  <si>
+    <t>spacewaves.co</t>
+  </si>
+  <si>
+    <t>core ball.com</t>
+  </si>
+  <si>
+    <t>core ball google doodle</t>
+  </si>
+  <si>
+    <t>coorball</t>
+  </si>
+  <si>
+    <t>google doodle core ball</t>
+  </si>
+  <si>
+    <t>core bal</t>
+  </si>
+  <si>
+    <t>pin circle games</t>
+  </si>
+  <si>
+    <t>how to beat coreball level 10</t>
+  </si>
+  <si>
+    <t>core ball apus</t>
+  </si>
+  <si>
+    <t>snow race 3d: fun racing</t>
+  </si>
+  <si>
+    <t>core ball online game</t>
+  </si>
+  <si>
+    <t>monkey type coreball</t>
+  </si>
+  <si>
+    <t>core ball game online</t>
+  </si>
+  <si>
+    <t>coreball cps test</t>
+  </si>
+  <si>
+    <t>p.1234 core ball</t>
+  </si>
+  <si>
+    <t>corn ball game online</t>
+  </si>
+  <si>
+    <t>core ball the game</t>
+  </si>
+  <si>
+    <t>unblocked coreball</t>
+  </si>
+  <si>
+    <t>core ball github.io</t>
+  </si>
+  <si>
+    <t>playspacewaves</t>
+  </si>
+  <si>
+    <t>co ball</t>
+  </si>
+  <si>
+    <t>coreball unblocked games</t>
+  </si>
+  <si>
+    <t>scratch core ball</t>
+  </si>
+  <si>
+    <t>cps test coreball</t>
+  </si>
+  <si>
+    <t>core ball unblocked games</t>
+  </si>
+  <si>
+    <t>core ba</t>
+  </si>
+  <si>
+    <t>coreball game online</t>
+  </si>
+  <si>
+    <t>circle pin game</t>
+  </si>
+  <si>
+    <t>coreball 2</t>
+  </si>
+  <si>
+    <t>unblocked core ball</t>
+  </si>
+  <si>
+    <t>cora ball game</t>
+  </si>
+  <si>
+    <t>care ball game</t>
+  </si>
+  <si>
+    <t>online scientific research core ball</t>
+  </si>
+  <si>
+    <t>core ball msn</t>
+  </si>
+  <si>
+    <t>best skill games</t>
+  </si>
+  <si>
+    <t>core ball free</t>
+  </si>
+  <si>
+    <t>coreball free</t>
+  </si>
+  <si>
+    <t>core ball online free</t>
+  </si>
+  <si>
+    <t>core ball browser</t>
+  </si>
+  <si>
+    <t>core ball web</t>
+  </si>
+  <si>
+    <t>core ball html5</t>
+  </si>
+  <si>
+    <t>core ball unblocked 66</t>
+  </si>
+  <si>
+    <t>core ball unblocked 911</t>
+  </si>
+  <si>
+    <t>core ball unblocked premium</t>
+  </si>
+  <si>
+    <t>core ball io</t>
+  </si>
+  <si>
+    <t>core ball levels</t>
+  </si>
+  <si>
+    <t>core ball level</t>
+  </si>
+  <si>
+    <t>core ball level 1</t>
+  </si>
+  <si>
+    <t>core ball level 2</t>
+  </si>
+  <si>
+    <t>core ball level 3</t>
+  </si>
+  <si>
+    <t>core ball level 4</t>
+  </si>
+  <si>
+    <t>core ball level 5</t>
+  </si>
+  <si>
+    <t>core ball level 10</t>
+  </si>
+  <si>
+    <t>core ball level 20</t>
+  </si>
+  <si>
+    <t>core ball level 30</t>
+  </si>
+  <si>
+    <t>core ball level 50</t>
+  </si>
+  <si>
+    <t>core ball level 99</t>
+  </si>
+  <si>
+    <t>core ball walkthrough</t>
+  </si>
+  <si>
+    <t>core ball guide</t>
+  </si>
+  <si>
+    <t>core ball tips</t>
+  </si>
+  <si>
+    <t>core ball tricks</t>
+  </si>
+  <si>
+    <t>core ball strategy</t>
+  </si>
+  <si>
+    <t>core ball how to play</t>
+  </si>
+  <si>
+    <t>how to play core ball</t>
+  </si>
+  <si>
+    <t>core ball controls</t>
+  </si>
+  <si>
+    <t>core ball gameplay</t>
+  </si>
+  <si>
+    <t>core ball play</t>
+  </si>
+  <si>
+    <t>core ball game free</t>
+  </si>
+  <si>
+    <t>core ball game free online</t>
+  </si>
+  <si>
+    <t>core ball game browser</t>
+  </si>
+  <si>
+    <t>core ball game html5</t>
+  </si>
+  <si>
+    <t>core ball challenge</t>
+  </si>
+  <si>
+    <t>core ball arcade</t>
+  </si>
+  <si>
+    <t>core ball puzzle</t>
+  </si>
+  <si>
+    <t>core ball skill game</t>
+  </si>
+  <si>
+    <t>core ball reflex game</t>
+  </si>
+  <si>
+    <t>core ball timing game</t>
+  </si>
+  <si>
+    <t>core ball spinning game</t>
+  </si>
+  <si>
+    <t>core ball pin game</t>
+  </si>
+  <si>
+    <t>core ball ball game</t>
+  </si>
+  <si>
+    <t>core ball endless</t>
+  </si>
+  <si>
+    <t>core ball classic</t>
+  </si>
+  <si>
+    <t>core ball original</t>
+  </si>
+  <si>
+    <t>core ball new</t>
+  </si>
+  <si>
+    <t>core ball mobile</t>
+  </si>
+  <si>
+    <t>core ball android</t>
+  </si>
+  <si>
+    <t>core ball ios</t>
+  </si>
+  <si>
+    <t>core ball app</t>
+  </si>
+  <si>
+    <t>core ball apk</t>
+  </si>
+  <si>
+    <t>core ball download</t>
+  </si>
+  <si>
+    <t>core ball no download</t>
+  </si>
+  <si>
+    <t>core ball fullscreen</t>
+  </si>
+  <si>
+    <t>core ball high score</t>
+  </si>
+  <si>
+    <t>core ball best score</t>
+  </si>
+  <si>
+    <t>core ball impossible</t>
+  </si>
+  <si>
+    <t>core ball easy</t>
+  </si>
+  <si>
+    <t>core ball hard</t>
+  </si>
+  <si>
+    <t>core ball expert</t>
+  </si>
+  <si>
+    <t>core ball all levels</t>
+  </si>
+  <si>
+    <t>core ball level guide</t>
+  </si>
+  <si>
+    <t>core ball cheats</t>
+  </si>
+  <si>
+    <t>core ball hacks</t>
+  </si>
+  <si>
+    <t>core ball solutions</t>
+  </si>
+  <si>
+    <t>core ball review</t>
+  </si>
+  <si>
+    <t>core ball wiki</t>
+  </si>
+  <si>
+    <t>core ball official</t>
+  </si>
+  <si>
+    <t>core ball website</t>
+  </si>
+  <si>
+    <t>core ball play online</t>
+  </si>
+  <si>
+    <t>play core ball online free</t>
+  </si>
+  <si>
+    <t>play core ball in browser</t>
+  </si>
+  <si>
+    <t>play core ball without download</t>
+  </si>
+  <si>
+    <t>free core ball game</t>
+  </si>
+  <si>
+    <t>free online core ball</t>
+  </si>
+  <si>
+    <t>online core ball game</t>
+  </si>
+  <si>
+    <t>coreball online free</t>
+  </si>
+  <si>
+    <t>coreball levels</t>
+  </si>
+  <si>
+    <t>coreball tips</t>
+  </si>
+  <si>
+    <t>coreball guide</t>
+  </si>
+  <si>
+    <t>coreball walkthrough</t>
+  </si>
+  <si>
+    <t>coreball controls</t>
+  </si>
+  <si>
+    <t>coreball gameplay</t>
+  </si>
+  <si>
+    <t>aa game</t>
+  </si>
+  <si>
+    <t>aa game online</t>
+  </si>
+  <si>
+    <t>aa ball game</t>
+  </si>
+  <si>
+    <t>knife hit</t>
+  </si>
+  <si>
+    <t>knife hit online</t>
+  </si>
+  <si>
+    <t>rotator game</t>
+  </si>
+  <si>
+    <t>looper game</t>
+  </si>
+  <si>
+    <t>color switch</t>
+  </si>
+  <si>
+    <t>core ball exercises</t>
+  </si>
+  <si>
+    <t>core ballet school</t>
+  </si>
+  <si>
+    <t>core ball workout</t>
+  </si>
+  <si>
+    <t>core ballet bozeman</t>
+  </si>
+  <si>
+    <t>core ballet</t>
+  </si>
+  <si>
+    <t>core ball aa</t>
+  </si>
+  <si>
+    <t>core ball 500 levels</t>
+  </si>
+  <si>
+    <t>core ball ensonhaber</t>
+  </si>
+  <si>
+    <t>aa core ball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">core ball game </t>
+  </si>
+  <si>
+    <t>Core ball classic</t>
+  </si>
+  <si>
+    <t>Core ball game</t>
+  </si>
+  <si>
+    <t>Core Ball GitHub</t>
+  </si>
+  <si>
+    <t>Google Core ball</t>
+  </si>
+  <si>
+    <t>Core Ball Scratch</t>
+  </si>
+  <si>
+    <t>Core ball monkey type</t>
+  </si>
+  <si>
+    <t>Core ball Baseball</t>
+  </si>
+  <si>
+    <t>Core ball weight</t>
   </si>
 </sst>
 </file>
@@ -2069,10 +1841,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A294"/>
+  <dimension ref="A1:A310"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="37.75" customWidth="1"/>
+    <col min="1" max="1" width="60.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" customHeight="1" spans="1:1">
@@ -2082,1467 +1854,1547 @@
     </row>
     <row r="2" ht="12.5" customHeight="1" spans="1:1">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="12.5" customHeight="1" spans="1:1">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="12.5" customHeight="1" spans="1:1">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="12.5" customHeight="1" spans="1:1">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="12.5" customHeight="1" spans="1:1">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="12.5" customHeight="1" spans="1:1">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="12.5" customHeight="1" spans="1:1">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="12.5" customHeight="1" spans="1:1">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="12.5" customHeight="1" spans="1:1">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="12.5" customHeight="1" spans="1:1">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="12.5" customHeight="1" spans="1:1">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="12.5" customHeight="1" spans="1:1">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="12.5" customHeight="1" spans="1:1">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="12.5" customHeight="1" spans="1:1">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" ht="12.5" customHeight="1" spans="1:1">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" ht="12.5" customHeight="1" spans="1:1">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="12.5" customHeight="1" spans="1:1">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" ht="12.5" customHeight="1" spans="1:1">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="12.5" customHeight="1" spans="1:1">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="12.5" customHeight="1" spans="1:1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" ht="12.5" customHeight="1" spans="1:1">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="12.5" customHeight="1" spans="1:1">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" ht="12.5" customHeight="1" spans="1:1">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" ht="12.5" customHeight="1" spans="1:1">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" ht="12.5" customHeight="1" spans="1:1">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" ht="12.5" customHeight="1" spans="1:1">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" ht="12.5" customHeight="1" spans="1:1">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" ht="12.5" customHeight="1" spans="1:1">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" ht="12.5" customHeight="1" spans="1:1">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" ht="12.5" customHeight="1" spans="1:1">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" ht="12.5" customHeight="1" spans="1:1">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" ht="12.5" customHeight="1" spans="1:1">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" ht="12.5" customHeight="1" spans="1:1">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" ht="12.5" customHeight="1" spans="1:1">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" ht="12.5" customHeight="1" spans="1:1">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" ht="12.5" customHeight="1" spans="1:1">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" ht="12.5" customHeight="1" spans="1:1">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" ht="12.5" customHeight="1" spans="1:1">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" ht="12.5" customHeight="1" spans="1:1">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" ht="12.5" customHeight="1" spans="1:1">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" ht="12.5" customHeight="1" spans="1:1">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" ht="12.5" customHeight="1" spans="1:1">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" ht="12.5" customHeight="1" spans="1:1">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" ht="12.5" customHeight="1" spans="1:1">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" ht="12.5" customHeight="1" spans="1:1">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" ht="12.5" customHeight="1" spans="1:1">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" ht="12.5" customHeight="1" spans="1:1">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" ht="12.5" customHeight="1" spans="1:1">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" ht="12.5" customHeight="1" spans="1:1">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" ht="12.5" customHeight="1" spans="1:1">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" ht="12.5" customHeight="1" spans="1:1">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" ht="12.5" customHeight="1" spans="1:1">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" ht="12.5" customHeight="1" spans="1:1">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" ht="12.5" customHeight="1" spans="1:1">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" ht="12.5" customHeight="1" spans="1:1">
       <c r="A56" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" ht="12.5" customHeight="1" spans="1:1">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" ht="12.5" customHeight="1" spans="1:1">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" ht="12.5" customHeight="1" spans="1:1">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" ht="12.5" customHeight="1" spans="1:1">
       <c r="A60" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" ht="12.5" customHeight="1" spans="1:1">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" ht="12.5" customHeight="1" spans="1:1">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" ht="12.5" customHeight="1" spans="1:1">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" ht="12.5" customHeight="1" spans="1:1">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" ht="12.5" customHeight="1" spans="1:1">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" ht="12.5" customHeight="1" spans="1:1">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" ht="12.5" customHeight="1" spans="1:1">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" ht="12.5" customHeight="1" spans="1:1">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" ht="12.5" customHeight="1" spans="1:1">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" ht="12.5" customHeight="1" spans="1:1">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" ht="12.5" customHeight="1" spans="1:1">
       <c r="A71" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72" ht="12.5" customHeight="1" spans="1:1">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" ht="12.5" customHeight="1" spans="1:1">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" ht="12.5" customHeight="1" spans="1:1">
       <c r="A74" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" ht="12.5" customHeight="1" spans="1:1">
       <c r="A75" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" ht="12.5" customHeight="1" spans="1:1">
       <c r="A76" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" ht="12.5" customHeight="1" spans="1:1">
       <c r="A77" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" ht="12.5" customHeight="1" spans="1:1">
       <c r="A78" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" ht="12.5" customHeight="1" spans="1:1">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" ht="12.5" customHeight="1" spans="1:1">
       <c r="A80" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" ht="12.5" customHeight="1" spans="1:1">
       <c r="A81" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82" ht="12.5" customHeight="1" spans="1:1">
       <c r="A82" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" ht="12.5" customHeight="1" spans="1:1">
       <c r="A83" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" ht="12.5" customHeight="1" spans="1:1">
       <c r="A84" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85" ht="12.5" customHeight="1" spans="1:1">
       <c r="A85" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
     </row>
     <row r="86" ht="12.5" customHeight="1" spans="1:1">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
     </row>
     <row r="87" ht="12.5" customHeight="1" spans="1:1">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" ht="12.5" customHeight="1" spans="1:1">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" ht="12.5" customHeight="1" spans="1:1">
       <c r="A89" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" ht="12.5" customHeight="1" spans="1:1">
       <c r="A90" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" ht="12.5" customHeight="1" spans="1:1">
       <c r="A91" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" ht="12.5" customHeight="1" spans="1:1">
       <c r="A92" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93" ht="12.5" customHeight="1" spans="1:1">
       <c r="A93" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94" ht="12.5" customHeight="1" spans="1:1">
       <c r="A94" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="95" ht="12.5" customHeight="1" spans="1:1">
       <c r="A95" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96" ht="12.5" customHeight="1" spans="1:1">
       <c r="A96" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" ht="12.5" customHeight="1" spans="1:1">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" ht="12.5" customHeight="1" spans="1:1">
       <c r="A98" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99" ht="12.5" customHeight="1" spans="1:1">
       <c r="A99" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
     </row>
     <row r="100" ht="12.5" customHeight="1" spans="1:1">
       <c r="A100" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101" ht="12.5" customHeight="1" spans="1:1">
       <c r="A101" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
     </row>
     <row r="102" ht="12.5" customHeight="1" spans="1:1">
       <c r="A102" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
     </row>
     <row r="103" ht="12.5" customHeight="1" spans="1:1">
       <c r="A103" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="104" ht="12.5" customHeight="1" spans="1:1">
       <c r="A104" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
     </row>
     <row r="105" ht="12.5" customHeight="1" spans="1:1">
       <c r="A105" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
     </row>
     <row r="106" ht="12.5" customHeight="1" spans="1:1">
       <c r="A106" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
     </row>
     <row r="107" ht="12.5" customHeight="1" spans="1:1">
       <c r="A107" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108" ht="12.5" customHeight="1" spans="1:1">
       <c r="A108" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
     </row>
     <row r="109" ht="12.5" customHeight="1" spans="1:1">
       <c r="A109" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
     </row>
     <row r="110" ht="12.5" customHeight="1" spans="1:1">
       <c r="A110" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
     </row>
     <row r="111" ht="12.5" customHeight="1" spans="1:1">
       <c r="A111" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" ht="12.5" customHeight="1" spans="1:1">
       <c r="A112" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
     </row>
     <row r="113" ht="12.5" customHeight="1" spans="1:1">
       <c r="A113" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
     </row>
     <row r="114" ht="12.5" customHeight="1" spans="1:1">
       <c r="A114" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
     </row>
     <row r="115" ht="12.5" customHeight="1" spans="1:1">
       <c r="A115" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
     </row>
     <row r="116" ht="12.5" customHeight="1" spans="1:1">
       <c r="A116" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
     </row>
     <row r="117" ht="12.5" customHeight="1" spans="1:1">
       <c r="A117" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
     </row>
     <row r="118" ht="12.5" customHeight="1" spans="1:1">
       <c r="A118" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
     </row>
     <row r="119" ht="12.5" customHeight="1" spans="1:1">
       <c r="A119" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
     </row>
     <row r="120" ht="12.5" customHeight="1" spans="1:1">
       <c r="A120" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
     </row>
     <row r="121" ht="12.5" customHeight="1" spans="1:1">
       <c r="A121" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="122" ht="12.5" customHeight="1" spans="1:1">
       <c r="A122" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
     </row>
     <row r="123" ht="12.5" customHeight="1" spans="1:1">
       <c r="A123" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
     </row>
     <row r="124" ht="12.5" customHeight="1" spans="1:1">
       <c r="A124" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
     </row>
     <row r="125" ht="12.5" customHeight="1" spans="1:1">
       <c r="A125" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
     </row>
     <row r="126" ht="12.5" customHeight="1" spans="1:1">
       <c r="A126" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127" ht="12.5" customHeight="1" spans="1:1">
       <c r="A127" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
     </row>
     <row r="128" ht="12.5" customHeight="1" spans="1:1">
       <c r="A128" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
     </row>
     <row r="129" ht="12.5" customHeight="1" spans="1:1">
       <c r="A129" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
     </row>
     <row r="130" ht="12.5" customHeight="1" spans="1:1">
       <c r="A130" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
     </row>
     <row r="131" ht="12.5" customHeight="1" spans="1:1">
       <c r="A131" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
     </row>
     <row r="132" ht="12.5" customHeight="1" spans="1:1">
       <c r="A132" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
     </row>
     <row r="133" ht="12.5" customHeight="1" spans="1:1">
       <c r="A133" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
     </row>
     <row r="134" ht="12.5" customHeight="1" spans="1:1">
       <c r="A134" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" ht="12.5" customHeight="1" spans="1:1">
       <c r="A135" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
     </row>
     <row r="136" ht="12.5" customHeight="1" spans="1:1">
       <c r="A136" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
     </row>
     <row r="137" ht="12.5" customHeight="1" spans="1:1">
       <c r="A137" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
     </row>
     <row r="138" ht="12.5" customHeight="1" spans="1:1">
       <c r="A138" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
     </row>
     <row r="139" ht="12.5" customHeight="1" spans="1:1">
       <c r="A139" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
     </row>
     <row r="140" ht="12.5" customHeight="1" spans="1:1">
       <c r="A140" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
     </row>
     <row r="141" ht="12.5" customHeight="1" spans="1:1">
       <c r="A141" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
     </row>
     <row r="142" ht="12.5" customHeight="1" spans="1:1">
       <c r="A142" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
     </row>
     <row r="143" ht="12.5" customHeight="1" spans="1:1">
       <c r="A143" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
     </row>
     <row r="144" ht="12.5" customHeight="1" spans="1:1">
       <c r="A144" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
     </row>
     <row r="145" ht="12.5" customHeight="1" spans="1:1">
       <c r="A145" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
     </row>
     <row r="146" ht="12.5" customHeight="1" spans="1:1">
       <c r="A146" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
     </row>
     <row r="147" ht="12.5" customHeight="1" spans="1:1">
       <c r="A147" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
     </row>
     <row r="148" ht="12.5" customHeight="1" spans="1:1">
       <c r="A148" t="s">
-        <v>139</v>
+        <v>74</v>
       </c>
     </row>
     <row r="149" ht="12.5" customHeight="1" spans="1:1">
       <c r="A149" t="s">
-        <v>140</v>
+        <v>75</v>
       </c>
     </row>
     <row r="150" ht="12.5" customHeight="1" spans="1:1">
       <c r="A150" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
     </row>
     <row r="151" ht="12.5" customHeight="1" spans="1:1">
       <c r="A151" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
     </row>
     <row r="152" ht="12.5" customHeight="1" spans="1:1">
       <c r="A152" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
     </row>
     <row r="153" ht="12.5" customHeight="1" spans="1:1">
       <c r="A153" t="s">
-        <v>144</v>
+        <v>76</v>
       </c>
     </row>
     <row r="154" ht="12.5" customHeight="1" spans="1:1">
       <c r="A154" t="s">
-        <v>145</v>
+        <v>77</v>
       </c>
     </row>
     <row r="155" ht="12.5" customHeight="1" spans="1:1">
       <c r="A155" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
     </row>
     <row r="156" ht="12.5" customHeight="1" spans="1:1">
       <c r="A156" t="s">
-        <v>147</v>
+        <v>79</v>
       </c>
     </row>
     <row r="157" ht="12.5" customHeight="1" spans="1:1">
       <c r="A157" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
     </row>
     <row r="158" ht="12.5" customHeight="1" spans="1:1">
       <c r="A158" t="s">
-        <v>149</v>
+        <v>81</v>
       </c>
     </row>
     <row r="159" ht="12.5" customHeight="1" spans="1:1">
       <c r="A159" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
     </row>
     <row r="160" ht="12.5" customHeight="1" spans="1:1">
       <c r="A160" t="s">
-        <v>151</v>
+        <v>83</v>
       </c>
     </row>
     <row r="161" ht="12.5" customHeight="1" spans="1:1">
       <c r="A161" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="162" ht="12.5" customHeight="1" spans="1:1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="163" ht="12.5" customHeight="1" spans="1:1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="164" ht="12.5" customHeight="1" spans="1:1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="165" ht="12.5" customHeight="1" spans="1:1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="166" ht="12.5" customHeight="1" spans="1:1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="167" ht="12.5" customHeight="1" spans="1:1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="168" ht="12.5" customHeight="1" spans="1:1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
       <c r="A168" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="169" ht="12.5" customHeight="1" spans="1:1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="170" ht="12.5" customHeight="1" spans="1:1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="171" ht="12.5" customHeight="1" spans="1:1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="172" ht="12.5" customHeight="1" spans="1:1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="173" ht="12.5" customHeight="1" spans="1:1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="174" ht="12.5" customHeight="1" spans="1:1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="175" ht="12.5" customHeight="1" spans="1:1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="176" ht="12.5" customHeight="1" spans="1:1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="177" ht="12.5" customHeight="1" spans="1:1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="178" ht="12.5" customHeight="1" spans="1:1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="179" ht="12.5" customHeight="1" spans="1:1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="180" ht="12.5" customHeight="1" spans="1:1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="181" ht="12.5" customHeight="1" spans="1:1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
       <c r="A181" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="182" ht="12.5" customHeight="1" spans="1:1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="183" ht="12.5" customHeight="1" spans="1:1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="184" ht="12.5" customHeight="1" spans="1:1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="185" ht="12.5" customHeight="1" spans="1:1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="186" ht="12.5" customHeight="1" spans="1:1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="187" ht="12.5" customHeight="1" spans="1:1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="188" ht="12.5" customHeight="1" spans="1:1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="189" ht="12.5" customHeight="1" spans="1:1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="190" ht="12.5" customHeight="1" spans="1:1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="191" ht="12.5" customHeight="1" spans="1:1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="192" ht="12.5" customHeight="1" spans="1:1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="193" ht="12.5" customHeight="1" spans="1:1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="194" ht="12.5" customHeight="1" spans="1:1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="195" ht="12.5" customHeight="1" spans="1:1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="196" ht="12.5" customHeight="1" spans="1:1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
       <c r="A196" t="s">
-        <v>185</v>
+        <v>32</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" t="s">
-        <v>5</v>
+        <v>108</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" t="s">
-        <v>187</v>
+        <v>112</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>191</v>
+        <v>117</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" t="s">
-        <v>194</v>
+        <v>120</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>195</v>
+        <v>121</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" t="s">
-        <v>196</v>
+        <v>122</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>197</v>
+        <v>123</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>198</v>
+        <v>124</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>199</v>
+        <v>125</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>200</v>
+        <v>126</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>203</v>
+        <v>129</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>208</v>
+        <v>135</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>209</v>
+        <v>136</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>210</v>
+        <v>137</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>211</v>
+        <v>138</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" t="s">
-        <v>212</v>
+        <v>139</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>213</v>
+        <v>140</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" t="s">
-        <v>214</v>
+        <v>141</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" t="s">
-        <v>215</v>
+        <v>142</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" t="s">
-        <v>85</v>
+        <v>143</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" t="s">
-        <v>216</v>
+        <v>144</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" t="s">
-        <v>217</v>
+        <v>145</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" t="s">
-        <v>219</v>
+        <v>147</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" t="s">
-        <v>220</v>
+        <v>148</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" t="s">
-        <v>0</v>
+        <v>149</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" t="s">
-        <v>221</v>
+        <v>151</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" t="s">
-        <v>222</v>
+        <v>152</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" t="s">
-        <v>224</v>
+        <v>154</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" t="s">
-        <v>225</v>
+        <v>155</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" t="s">
-        <v>226</v>
+        <v>156</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" t="s">
-        <v>227</v>
+        <v>157</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" t="s">
-        <v>228</v>
+        <v>158</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" t="s">
-        <v>24</v>
+        <v>159</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" t="s">
-        <v>229</v>
+        <v>160</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" t="s">
-        <v>231</v>
+        <v>162</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" t="s">
-        <v>232</v>
+        <v>163</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" t="s">
-        <v>233</v>
+        <v>76</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" t="s">
-        <v>235</v>
+        <v>165</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" t="s">
-        <v>236</v>
+        <v>166</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" t="s">
-        <v>237</v>
+        <v>167</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" t="s">
-        <v>238</v>
+        <v>168</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" t="s">
-        <v>239</v>
+        <v>169</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" t="s">
-        <v>244</v>
+        <v>34</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" t="s">
-        <v>245</v>
+        <v>43</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" t="s">
-        <v>247</v>
+        <v>175</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" t="s">
-        <v>248</v>
+        <v>176</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" t="s">
-        <v>249</v>
+        <v>177</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" t="s">
-        <v>250</v>
+        <v>178</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" t="s">
-        <v>251</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" t="s">
-        <v>252</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" t="s">
-        <v>253</v>
+        <v>179</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" t="s">
-        <v>254</v>
+        <v>24</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" t="s">
-        <v>255</v>
+        <v>180</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" t="s">
-        <v>256</v>
+        <v>181</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" t="s">
-        <v>257</v>
+        <v>62</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" t="s">
-        <v>258</v>
+        <v>182</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" t="s">
-        <v>259</v>
+        <v>183</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" t="s">
-        <v>260</v>
+        <v>184</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" t="s">
-        <v>261</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" t="s">
-        <v>262</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" t="s">
-        <v>263</v>
+        <v>179</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" t="s">
-        <v>264</v>
+        <v>24</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" t="s">
-        <v>265</v>
+        <v>181</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" t="s">
-        <v>266</v>
+        <v>62</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" t="s">
-        <v>267</v>
+        <v>184</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" t="s">
-        <v>268</v>
+        <v>185</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" t="s">
-        <v>269</v>
+        <v>33</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" t="s">
-        <v>270</v>
+        <v>46</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" t="s">
-        <v>271</v>
+        <v>186</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" t="s">
-        <v>272</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/关键词.xlsx
+++ b/关键词.xlsx
@@ -2,39 +2,368 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="20">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +371,308 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1025,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -413,524 +1034,919 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A74"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A130"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col width="69.75" customWidth="1" style="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>acceleration city</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>acceleration game</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker female</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>acceleration city 2</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker unblocked</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>acceleration city 3</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker game</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>acceleration cities</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>what is bear clicker</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>city acceleration</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>female bear clicker</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>acceleration games</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker female version</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>acceleration city game</t>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>girl bear clicker</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>acceleration city hour of code</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker 2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hour of code acceleration city</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker.com</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>acceleration car game</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker girl version unblocked</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>acceleration city car game</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker 3</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>acceleration city cs stem network</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>who made bear clicker</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>acceleration city cs-stem network</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker game unblocked</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>acceleration city cs stem</t>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker sus</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>acceleration city code.org</t>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>gummy bear clicker</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>code.org acceleration city</t>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>the bear clicker</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>acceleration station</t>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker girl</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>acceleration city hour of code free</t>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>games like bear clicker</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>acceleration city download</t>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>mama bear clicker</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>acceleration city map</t>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>polar bear clicker</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>acceleration city coding</t>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>teddy bear clicker</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>acceleration city i cs-stem</t>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker girl version</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>hour of code games acceleration city</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker girl free</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>hour of ai acceleration city</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker co</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>car acceleration city</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker scratch</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>can you play acceleration city on ipad</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker meaning</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>acc acceleration city</t>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker woman</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>math playground acceleration city</t>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>clicker game</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>acceleration city mobile</t>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>games</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>acceleration city online</t>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>clicker games</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>acceleration city play</t>
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>cookie clicker</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>play acceleration city</t>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>girl clicker</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>acceleration city free</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Baby bear clicker</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>acceleration city browser</t>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>bearing clicker</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>acceleration city html5</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>bearded dragon clicker</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>acceleration city game online</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>play bear clicker</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>acceleration city unblocked</t>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>play bear clicker online</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>acceleration city unblocked games</t>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>play bear clicker free</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>acceleration city unblocked 66</t>
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker online</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>acceleration city unblocked 76</t>
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker free</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>acceleration city classroom</t>
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker browser</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>acceleration city school</t>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker browser game</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>acceleration city at school</t>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker web game</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>acceleration city cs2n</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker html5</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>cs2n acceleration city</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker unblocked games</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>acceleration city stem</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker unblocked 76</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>acceleration city robotics</t>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker unblocked 66</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>acceleration city science</t>
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker io</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>acceleration city engineering</t>
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker game online</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>acceleration city educational game</t>
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker online game</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>acceleration city gameplay</t>
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker clicker game</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>acceleration city walkthrough</t>
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker idle game</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>acceleration city guide</t>
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker incremental game</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>acceleration city tutorial</t>
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker simulator</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>acceleration city controls</t>
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker adventure</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>acceleration city levels</t>
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker classic</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>acceleration city challenge</t>
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker original</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>acceleration city tips</t>
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker remake</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>acceleration city tricks</t>
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker deluxe</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>acceleration city strategy</t>
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker new version</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>how to play acceleration city</t>
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker latest version</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>how to beat acceleration city</t>
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker update</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>acceleration city pc</t>
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker mobile</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>acceleration city ipad</t>
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker android</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>acceleration city tablet</t>
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker ios</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>acceleration city chrome</t>
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker iphone</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>acceleration city latest</t>
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker ipad</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>acceleration city new version</t>
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker pc</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>acceleration city flash</t>
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker desktop</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>acceleration city apk</t>
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker windows</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>acceleration city exe</t>
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker mac</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>acceleration city treasure hunters game</t>
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker chrome</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>acceleration of honda city</t>
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker download</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker apk</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker apk download</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker install</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker walkthrough</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker tricks</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker tutorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker gameplay</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker how to play</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker wiki</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker faq</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker achievements</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker secrets</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker upgrades</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker rewards</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker redeem codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker cheats</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker hack</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker mods</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker mod apk</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>games similar to bear clicker</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>bear games</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>animal clicker</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>animal clicker game</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>pet clicker</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>pet clicker game</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>cute clicker game</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>idle clicker game</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>tap clicker game</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>idle games</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>incremental games</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker official</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker official website</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker website</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>play bear clicker online for free</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>play bear clicker in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>play bear clicker without download</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker no download</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker free online game</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker html5 game</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker browser game free</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker at school</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>bear clicker for kids</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>best bear clicker strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>how to play bear clicker</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>is bear clicker free</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>can i play bear clicker online</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>where to play bear clicker</t>
         </is>
       </c>
     </row>

--- a/关键词.xlsx
+++ b/关键词.xlsx
@@ -16,7 +16,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -471,155 +478,155 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1034,919 +1041,1444 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A130"/>
+  <dimension ref="A1:A205"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="69.75" customWidth="1" style="1" min="1" max="1"/>
+    <col width="63.875" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>bear clicker</t>
+          <t>football bros</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bear clicker female</t>
+          <t>football bros io</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bear clicker unblocked</t>
+          <t>football bros game</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bear clicker game</t>
+          <t>football bros.io</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>what is bear clicker</t>
+          <t>football bros g+</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>female bear clicker</t>
+          <t>football bros game unblocked</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bear clicker female version</t>
+          <t>football bros crazy games</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>girl bear clicker</t>
+          <t>football bros official site</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bear clicker 2</t>
+          <t>football bros'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bear clicker.com</t>
+          <t>football bros college</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bear clicker girl version unblocked</t>
+          <t>football bros online</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bear clicker 3</t>
+          <t>football bros games</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>who made bear clicker</t>
+          <t>college football bros game</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bear clicker game unblocked</t>
+          <t>football bros run</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bear clicker sus</t>
+          <t>football bros space</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>gummy bear clicker</t>
+          <t>football bros io unblocked</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>the bear clicker</t>
+          <t>g+ football bros</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bear clicker girl</t>
+          <t>football brose</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>games like bear clicker</t>
+          <t>football bros.run</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>mama bear clicker</t>
+          <t>football bros .io</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>polar bear clicker</t>
+          <t>football bros io game</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>teddy bear clicker</t>
+          <t>g football bros</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bear clicker girl version</t>
+          <t>google doodle games football bros</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bear clicker girl free</t>
+          <t>football bross</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bear clicker co</t>
+          <t>football bros .com</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bear clicker scratch</t>
+          <t>football bros mobile</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bear clicker meaning</t>
+          <t>football bros]</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bear clicker woman</t>
+          <t>football bros com</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>clicker game</t>
+          <t>football bros i o</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>football bros g</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>clicker games</t>
+          <t>football bros.com</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>cookie clicker</t>
+          <t>football bros free</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>girl clicker</t>
+          <t>football bros dunk beauty</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Baby bear clicker</t>
+          <t>football bros 1 games</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bearing clicker</t>
+          <t>6x football bros</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bearded dragon clicker</t>
+          <t>football bros html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>play bear clicker</t>
+          <t>football bros github io</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>play bear clicker online</t>
+          <t>football bros . io</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>play bear clicker free</t>
+          <t>football bros official</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bear clicker online</t>
+          <t>football bros g plus</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bear clicker free</t>
+          <t>football bros game online</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bear clicker browser</t>
+          <t>who made football bros</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bear clicker browser game</t>
+          <t>g+football bros</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bear clicker web game</t>
+          <t>play football bros</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bear clicker html5</t>
+          <t>football bros msn</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bear clicker unblocked games</t>
+          <t>football bros.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bear clicker unblocked 76</t>
+          <t>football bros.me</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bear clicker unblocked 66</t>
+          <t>what is the best team in football bros io</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bear clicker io</t>
+          <t>football bros online game</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bear clicker game online</t>
+          <t>football bros.online</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bear clicker online game</t>
+          <t>football bros .run</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bear clicker clicker game</t>
+          <t>https football bros io</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bear clicker idle game</t>
+          <t>football bros gitlab</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bear clicker incremental game</t>
+          <t>how to play football bros</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bear clicker simulator</t>
+          <t>american football bros</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bear clicker adventure</t>
+          <t>football bros best team</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bear clicker classic</t>
+          <t>college football bros</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bear clicker original</t>
+          <t>football bros unblocked games</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bear clicker remake</t>
+          <t>unblocked football bros</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bear clicker deluxe</t>
+          <t>fb.dunk.beauty football bros</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bear clicker new version</t>
+          <t>football bros unblocked game</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bear clicker latest version</t>
+          <t>football bros github</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bear clicker update</t>
+          <t>football bros cheats</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bear clicker mobile</t>
+          <t>football bros me</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bear clicker android</t>
+          <t>classroom center football bros</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bear clicker ios</t>
+          <t>what are the controls for football bros</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bear clicker iphone</t>
+          <t>football bros google doodle</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bear clicker ipad</t>
+          <t>football bros free online soccer game</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bear clicker pc</t>
+          <t>football bros unlocked</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bear clicker desktop</t>
+          <t>crispy clean football bros</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bear clicker windows</t>
+          <t>football bros unblocked 66</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bear clicker mac</t>
+          <t>controls for football bros</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bear clicker chrome</t>
+          <t>football bros 6x</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bear clicker download</t>
+          <t>football bros.org</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bear clicker apk</t>
+          <t>football bros hacks</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bear clicker apk download</t>
+          <t>football bros controls</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bear clicker install</t>
+          <t>history surf football bros</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bear clicker guide</t>
+          <t>football bros download</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bear clicker walkthrough</t>
+          <t>dunk beauty football bros</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bear clicker tips</t>
+          <t>how to throw in football bros</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bear clicker tricks</t>
+          <t>www history surf football bros</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bear clicker strategy</t>
+          <t>football bros unblocked</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bear clicker tutorial</t>
+          <t>football bros unblocked 76</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bear clicker gameplay</t>
+          <t>football bros classroom 6x</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bear clicker controls</t>
+          <t>google doodle football bros</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bear clicker how to play</t>
+          <t>football bros unblocked g+</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bear clicker wiki</t>
+          <t>unblocked games football bros</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bear clicker faq</t>
+          <t>football bros google sites</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bear clicker achievements</t>
+          <t>football bros unblocked games g+</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bear clicker secrets</t>
+          <t>football bros classroom center</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bear clicker levels</t>
+          <t>football bros unblocked g</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bear clicker upgrades</t>
+          <t>football bros crispy clean</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bear clicker rewards</t>
+          <t>collage football bros</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bear clicker codes</t>
+          <t>football bros unblocked github</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bear clicker redeem codes</t>
+          <t>football bros unblocked 67</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bear clicker cheats</t>
+          <t>football bros online unblocked</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bear clicker hack</t>
+          <t>football bros unblocked classroom 6x</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>bear clicker mods</t>
+          <t>classroom 6x football bros</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bear clicker mod apk</t>
+          <t>what is the best team in football bros</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>games similar to bear clicker</t>
+          <t>best team in football bros</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bear games</t>
+          <t>fb dunk beauty football bros</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>animal clicker</t>
+          <t>football bros google classroom</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>animal clicker game</t>
+          <t>football bros cheerleader</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>pet clicker</t>
+          <t>football bros unblocked google classroom</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>pet clicker game</t>
+          <t>football bros play</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>cute clicker game</t>
+          <t>football bros free online</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>idle clicker game</t>
+          <t>football bros game free</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>tap clicker game</t>
+          <t>football bros free play</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>idle games</t>
+          <t>football bros browser game</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>incremental games</t>
+          <t>football bros web game</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bear clicker developer</t>
+          <t>football bros football game</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bear clicker publisher</t>
+          <t>football bros website</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bear clicker studio</t>
+          <t>football bros developer</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>bear clicker official</t>
+          <t>football bros creator</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bear clicker official website</t>
+          <t>who made football bros game</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bear clicker website</t>
+          <t>football bros studio</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>play bear clicker online for free</t>
+          <t>football bros gameplay</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>play bear clicker in browser</t>
+          <t>football bros guide</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>play bear clicker without download</t>
+          <t>football bros walkthrough</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bear clicker no download</t>
+          <t>football bros tutorial</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bear clicker free online game</t>
+          <t>football bros tips</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bear clicker html5 game</t>
+          <t>football bros tricks</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bear clicker browser game free</t>
+          <t>football bros strategy</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bear clicker at school</t>
+          <t>football bros how to play</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bear clicker for kids</t>
+          <t>football bros review</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>best bear clicker strategy</t>
+          <t>football bros mechanics</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>how to play bear clicker</t>
+          <t>football bros 2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>is bear clicker free</t>
+          <t>football bros 3</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>can i play bear clicker online</t>
+          <t>football bros latest version</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>where to play bear clicker</t>
+          <t>football bros new version</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>football bros update</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>football bros beta</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>football bros old version</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>football bros 2 player</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>football bros multiplayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>football bros online multiplayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>football bros local multiplayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>football bros coop</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>football bros versus</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>football bros vs friends</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>football bros split screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>football bros at school</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>football bros school</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>football bros classroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>football bros play at school</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>football bros no download</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>football bros no install</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>football bros browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>football bros android</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>football bros ios</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>football bros pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>football bros windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>football bros mac</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>football bros chromebook</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>football bros steam</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>football bros apk</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>football bros app</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>football bros install</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>football bros exe</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>football bros poki</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>football bros itch io</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>football bros github pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>football bros full screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>football bros full screen game</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>football bros leaderboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>football bros rankings</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>football bros franchise</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>football bros season mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>football bros tournament</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>football bros championship</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>football bros roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>football bros teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>football bros characters</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>football bros skins</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>football bros mods</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>football bros achievements</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>football bros settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>football bros controls pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>football bros keyboard controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>football bros controller support</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>football bros lag</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>football bros not working</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>football bros bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>football bros update notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>football bros patch notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>football bros wiki</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>football bros faq</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>is football bros free</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>is football bros multiplayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>is football bros online</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>is football bros on mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>is football bros on pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>can you play football bros online</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>where to play football bros</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>games like football bros</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>best games like football bros</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>football games</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>american football games</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>online football games</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>2 player football games</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>arcade football games</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>retro football games</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>pixel football games</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>football io games</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>multiplayer football games</t>
         </is>
       </c>
     </row>

--- a/关键词.xlsx
+++ b/关键词.xlsx
@@ -16,14 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -478,157 +471,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1044,821 +1034,492 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A116"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="75.5" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked 76</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked games</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked games</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked mods</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked classroom</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked 911</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked classroom 6x</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked 76</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked 66</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>darkness takeover fnf unblocked</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked full screen</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked game</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked games g+</t>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked indie cross</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked 67</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>silly billy fnf unblocked</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked 6x</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked wtf</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked 76 classroom 6x</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked week 8</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked github</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>indie cross fnf unblocked</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked games 76</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked silly billy</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked games world</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked sites</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked game</t>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked school</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked google classroom</t>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked online</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked classroom games</t>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked 66</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked google sites</t>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked mobile</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked.github.io</t>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked'</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked on hooda math</t>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked mod</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked hooda math</t>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked week 6</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked gitlab</t>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked websites</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>snow rider unblocked</t>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>week 7 fnf unblocked</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked online</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked free</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked free</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>play fnf unblocked</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>play snow rider 3d unblocked</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked tricky</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked play</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked among us</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked browser</t>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked at school</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked web</t>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>zardy fnf unblocked</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked html5</t>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked github</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked no download</t>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked google sites</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked fullscreen</t>
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked full screen</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked mobile</t>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>FNF unblocked snokido</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked android</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>FNF unblocked KBH</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked ios</t>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>friday night funkin unblocked</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked ipad</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>fnf game unblocked</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked pc</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>fnf online</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked chromebook</t>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>fnf browser</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked at school</t>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>fnf browser game</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked for school</t>
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>fnf web</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked github io</t>
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>fnf html5</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked 77</t>
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>fnf online free</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked 911</t>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>fnf no download</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked 6969</t>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>fnf unblocked for school</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked original</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>fnf school game</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked official</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>fnf classroom</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked endless</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>fnf classroom 6x</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked arcade</t>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>fnf classroom games</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked winter</t>
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>fnf mods</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked sled</t>
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs sonic exe</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked sledding</t>
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs huggy wuggy</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked high score</t>
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs shaggy</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked world record</t>
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs impostor</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked controls</t>
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs tabi</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked tips</t>
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs whitty</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked guide</t>
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs garcello</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked walkthrough</t>
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs tricky</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked gameplay</t>
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs hex</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked cheats</t>
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs matt</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked hacks</t>
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs miku</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked free online</t>
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>fnf vs qt</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>snow rider 3d unblocked online free</t>
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>fnf corruption</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>best snow rider 3d unblocked</t>
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>fnf b sides</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>new snow rider 3d unblocked</t>
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>fnf neo</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>classic snow rider 3d unblocked</t>
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>fnf indie cross</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>snow rider 3d</t>
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>fnf pibby</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>snow rider 3d game</t>
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>fnf mario madness</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>snow rider game</t>
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>fnf dave and bambi</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>snow rider</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>snow rider online</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>snow rider 3d online</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>play snow rider 3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>play snow rider</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>snow rider 3d free</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>snow rider free</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>snow rider 3d online free</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>snow rider 3d browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>snow rider browser game</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>snow rider 3d html5</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>snow rider web game</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>snow rider 3d mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>snow rider 3d android</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>snow rider 3d ios</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>snow rider 3d ipad</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>snow rider 3d pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>snow rider 3d chromebook</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>snow rider 3d laptop</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>snow rider 3d fullscreen</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>snow rider 3d no download</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>snow rider 3d download</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>snow rider 3d original</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>snow rider 3d official</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>snow rider 3d endless</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>snow rider 3d arcade</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>snow rider 3d winter</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>snow rider 3d snowboarding</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>snow rider 3d sled</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>snow rider 3d sledding</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>snow rider 3d ski game</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>snow rider 3d christmas</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>snow rider 3d holiday</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>snow rider 3d gameplay</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>snow rider 3d trailer</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>snow rider 3d controls</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>snow rider 3d guide</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>snow rider 3d tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>snow rider 3d walkthrough</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>snow rider 3d cheats</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>snow rider 3d hacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>snow rider 3d high score</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>snow rider 3d world record</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>snow rider 3d multiplayer</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>snow rider 3d single player</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>best snow rider 3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>new snow rider 3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>classic snow rider 3d</t>
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>fnf sonic exe</t>
         </is>
       </c>
     </row>
